--- a/_sources/cdifProperties/cdifDataDescription/cdifDataDescription_properties.xlsx
+++ b/_sources/cdifProperties/cdifDataDescription/cdifDataDescription_properties.xlsx
@@ -7,10 +7,14 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cdifDataDescription" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="statisticalVariable" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="definedTerm" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="identifier" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="propertyTree" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cdifDataDescription" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cdifVariableMeasured" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cdifDataCube" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cdifTabularData" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="definedTerm" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cdifPhysicalMapping" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="identifier" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,6 +35,9 @@
     <font>
       <b val="1"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="3">
@@ -59,13 +66,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -432,6 +442,928 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:G82"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="6" max="6"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>property</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>object/data type</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>property</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>object/data type</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>property</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>object/datatype</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>cdifDataDescription</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>schema:subjectOf</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>dcterms:conformsTo</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>[object]</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>@id</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>string (must contain dataDescription/1.0/)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>@context</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>csvw</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>const: http://www.w3.org/ns/csvw#</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>schema:variableMeasured</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>[cdifVariableMeasured]</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>@id</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>string (required)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>@type</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>[string] (must contain cdi:InstanceVariable)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>cdi:physicalDataType</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>[string | object ref | DefinedTerm]</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>cdi:intendedDataType</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>cdi:role</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>string (enum)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>MeasureComponent</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>AttributeComponent</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>DimensionComponent</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>DescriptorComponent</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>ReferenceValueComponent</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>cdi:describedUnitOfMeasure</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>DefinedTerm</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>cdi:simpleUnitOfMeasure</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>object reference</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>@id</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>DefinedTerm</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>cdi:uses</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>[string]</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>[object reference]</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>@id</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>[DefinedTerm]</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>cdi:name</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>cdi:displayLabel</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>cdi:identifier</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>(also includes)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>variableMeasured (PropertyValue)</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>statisticalVariable</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>schema:distribution</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>[object]</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>cdi:characterSet</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>cdi:fileSize</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>cdi:fileSizeUofM</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>(anyOf)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>[cdifTabularData]</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>@type</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>[string] (must contain cdi:TabularTextDataSet)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>cdi:isDelimited</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>cdi:isFixedWidth</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>csvw:delimiter</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>csvw:header</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>csvw:headerRowCount</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>csvw:skipRows</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>csvw:commentPrefix</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>csvw:quoteChar</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>csvw:lineTerminators</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>csvw:skipBlankRows</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>csvw:skipColumns</t>
+        </is>
+      </c>
+      <c r="G55" s="3" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>csvw:skipInitialSpace</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>csvw:trim</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>csvw:tableDirection</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t>csvw:textDirection</t>
+        </is>
+      </c>
+      <c r="G59" s="3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t>cdi:escapeCharacter</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="F61" s="3" t="inlineStr">
+        <is>
+          <t>cdi:headerIsCaseSensitive</t>
+        </is>
+      </c>
+      <c r="G61" s="3" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t>cdi:treatConsecutiveDelimitersAsOne</t>
+        </is>
+      </c>
+      <c r="G62" s="3" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="F63" s="3" t="inlineStr">
+        <is>
+          <t>cdi:hasPhysicalMapping</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="G64" s="3" t="inlineStr">
+        <is>
+          <t>[cdifPhysicalMapping]</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>[cdifDataCube]</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="F66" s="3" t="inlineStr">
+        <is>
+          <t>@type</t>
+        </is>
+      </c>
+      <c r="G66" s="3" t="inlineStr">
+        <is>
+          <t>[string] (must contain cdi:StructuredDataSet)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="F67" s="3" t="inlineStr">
+        <is>
+          <t>cdi:hasPhysicalMapping</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="G68" s="3" t="inlineStr">
+        <is>
+          <t>[cdifPhysicalMapping]</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="E69" s="3" t="inlineStr">
+        <is>
+          <t>[any]</t>
+        </is>
+      </c>
+      <c r="G69" s="3" t="inlineStr">
+        <is>
+          <t>(no additional constraints)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>cdifPhysicalMapping</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>cdi:index</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>cdi:format</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>cdi:physicalDataType</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>cdi:length</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>cdi:nullSequence</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>cdi:defaultValue</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>cdi:scale</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>cdi:decimalPositions</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>cdi:minimumLength</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>cdi:maximumLength</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="D81" s="3" t="inlineStr">
+        <is>
+          <t>cdi:isRequired</t>
+        </is>
+      </c>
+      <c r="E81" s="3" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="D82" s="3" t="inlineStr">
+        <is>
+          <t>cdi:formats_InstanceVariable</t>
+        </is>
+      </c>
+      <c r="E82" s="3" t="inlineStr">
+        <is>
+          <t>object reference</t>
+        </is>
+      </c>
+      <c r="F82" s="3" t="inlineStr">
+        <is>
+          <t>@id</t>
+        </is>
+      </c>
+      <c r="G82" s="3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -553,17 +1485,12 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>array of object | statisticalVariable</t>
+          <t>array of object reference &amp; cdifVariableMeasured</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
           <t>0..*</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>@type: must contain: cdi:InstanceVariable</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -590,7 +1517,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>array of object</t>
+          <t>array of object &amp; cdifDataCube | cdifTabularData | any</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -609,13 +1536,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -672,7 +1599,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>schema:StatisticalVariable</t>
+          <t>cdi:InstanceVariable</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -687,19 +1614,24 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>must contain: schema:StatisticalVariable</t>
+          <t>must contain: cdi:InstanceVariable</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Must include both schema:PropertyValue and cdi:InstanceVariable. Additional types may be included.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>@id</t>
+          <t>cdi:identifier</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>schema:StatisticalVariable</t>
+          <t>cdi:InstanceVariable</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -716,49 +1648,39 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>schema:name</t>
+          <t>cdi:physicalDataType</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>schema:StatisticalVariable</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Title</t>
+          <t>cdi:InstanceVariable</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>array of string | object reference | definedTerm</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0..*</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>string label for the statistical variable</t>
+          <t>identifier or name for the data type concept.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>schema:description</t>
+          <t>cdi:intendedDataType</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>schema:StatisticalVariable</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Description</t>
+          <t>cdi:InstanceVariable</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -769,50 +1691,60 @@
       <c r="E5" s="2" t="inlineStr">
         <is>
           <t>0..1</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>The intended data type for values of this variable, from DDI-CDI RepresentedVariable.hasIntendedDataType. Recommended values are XML Schema datatypes (e.g. https://www.w3.org/TR/xmlschema-2/#decimal).</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>schema:alternateName</t>
+          <t>cdi:role</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>schema:StatisticalVariable</t>
+          <t>cdi:InstanceVariable</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>array of string</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0..*</t>
+          <t>0..1</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>MeasureComponent, AttributeComponent, DimensionComponent, DescriptorComponent, ReferenceValueComponent</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>An alias for the item (Alternative names that have been used to refer to this dataset, such as aliases or abbreviations.). Not in current recommendation, implemenation suggested here.</t>
+          <t>Specifies the relation of the variable to the data structure, corresponding to DDI-CDI DataStructureComponent subtypes.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>schema:measurementTechnique</t>
+          <t>cdi:describedUnitOfMeasure</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>schema:StatisticalVariable</t>
+          <t>cdi:InstanceVariable</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>string | object | definedTerm</t>
+          <t>definedTerm</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -822,24 +1754,24 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Text description or URI identifying the measurement method.</t>
+          <t>A structured unit of measure from a controlled vocabulary, from DDI-CDI RepresentedVariable.describedUnitOfMeasure.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>schema:statType</t>
+          <t>cdi:simpleUnitOfMeasure</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>schema:StatisticalVariable</t>
+          <t>cdi:InstanceVariable</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>string | object | definedTerm</t>
+          <t>string | object reference | definedTerm</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -851,28 +1783,81 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>schema:measuredProperty</t>
+          <t>cdi:uses</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>schema:StatisticalVariable</t>
+          <t>cdi:InstanceVariable</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>array of string | object reference | definedTerm</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>@type: const: schema:Property
-must contain: schema:Property</t>
+          <t>0..*</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Essentially the same as schema:propertyID. References to concepts that this variable measures or represents.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>cdi:name</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>cdi:InstanceVariable</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0..1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>DDI-CDI Concept.name. The name of this variable in the DDI-CDI model.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>cdi:displayLabel</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>cdi:InstanceVariable</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0..1</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>DDI-CDI Concept.displayLabel. A human-readable label for display purposes.</t>
         </is>
       </c>
     </row>
@@ -881,7 +1866,829 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="80" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Field Name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Containing Class</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>CDIF Content Model</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Data Type(s)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Cardinality</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Enum/Const Values</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>@type</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Data Cube Type</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>any</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>0..*</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>must contain: cdi:StructuredDataSet</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>cdi:hasPhysicalMapping</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Data Cube Type</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>array of cdifPhysicalMapping &amp; object</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>0..*</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Links variables to their physical representation in this dataset.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="80" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Field Name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Containing Class</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>CDIF Content Model</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Data Type(s)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Cardinality</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Enum/Const Values</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>@type</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Tabular Data Type</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>any</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>2..*</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>must contain: cdi:TabularTextDataSet</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>cdi:arrayBase</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Tabular Data Type</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>0..1</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>csvw:commentPrefix</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Tabular Data Type</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0..1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>An atomic property that sets the comment prefix flag to the single provided value, which MUST be a string. The default is '#'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>csvw:delimiter</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Tabular Data Type</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0..1</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Sets the delimiter flag to the single provided value, which MUST be a string. The default is ','.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>csvw:header</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Tabular Data Type</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0..1</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>If true, sets the header row count flag to 1, and if false to 0, unless headerRowCount is provided, in which case the value provided for the header property is ignored. The default is true.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>csvw:headerRowCount</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Tabular Data Type</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0..1</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>default: 1</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>A numeric atomic property that sets the header row count flag to the single provided value, which MUST be a non-negative integer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>cdi:isDelimited</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Tabular Data Type</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0..1</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Schema constraint is that one of {'isDelimited','isFixedWidth'} must be present with a True value; the other one may be present or omitted, but if present must have a false value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>cdi:isFixedWidth</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Tabular Data Type</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0..1</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>csvw:lineTerminators</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Tabular Data Type</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0..1</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CRLF, LF, 
+, 
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>csvw:quoteChar</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Tabular Data Type</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0..1</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>default: "</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Same as DDI-CDI quoteCharacter. The string that is used around escaped cells.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>csvw:skipBlankRows</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Tabular Data Type</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0..1</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>default: False</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>csvw:skipColumns</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Tabular Data Type</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0..1</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>default: 0</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>The number of columns to skip at the beginning of each row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>csvw:skipInitialSpace</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Tabular Data Type</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0..1</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>default: True</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>csvw:skipRows</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Tabular Data Type</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>0..1</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>default: 0</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>The number of rows to skip at the beginning of the file, before a header row or tabular data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>cdi:escapeCharacter</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Tabular Data Type</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0..1</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>The character used to escape special characters in the data. From DDI-CDI PhysicalSegmentLayout.escapeCharacter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>cdi:headerIsCaseSensitive</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Tabular Data Type</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0..1</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>default: False</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Whether column header names are case-sensitive. From DDI-CDI PhysicalSegmentLayout.headerIsCaseSensitive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>cdi:treatConsecutiveDelimitersAsOne</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Tabular Data Type</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>0..1</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>default: False</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>Whether consecutive delimiters should be treated as a single delimiter. From DDI-CDI PhysicalSegmentLayout.treatConsecutiveDelimitersAsOne.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>csvw:tableDirection</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Tabular Data Type</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0..1</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Ltr, Rtl</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>Indicates the direction of the table layout (left-to-right or right-to-left). From DDI-CDI PhysicalSegmentLayout.tableDirection.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>csvw:textDirection</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Tabular Data Type</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0..1</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Auto, Inherit, Ltr, Rtl</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>Indicates whether the text within cells should be displayed as left-to-right, right-to-left, according to content, or inherited from the table direction. From DDI-CDI PhysicalSegmentLayout.textDirection.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>csvw:trim</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Tabular Data Type</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>0..1</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>true, end, false, start</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>Indicates whether to trim whitespace around cells. 'true' corresponds to DDI-CDI 'both' value, 'false' corresponds to DDI-CDI 'neither' value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>cdi:hasPhysicalMapping</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Tabular Data Type</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>array of cdifPhysicalMapping</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>0..*</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>Links variables to their physical representation in this dataset.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>countRows</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Tabular Data Type</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>0..1</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>countColumns</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Tabular Data Type</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>0..1</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -949,18 +2756,17 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>const | array of string</t>
+          <t>array of string</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1..*</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>const: schema:DefinedTerm
-must contain: schema:DefinedTerm</t>
+          <t>must contain: schema:DefinedTerm</t>
         </is>
       </c>
     </row>
@@ -1087,7 +2893,366 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="80" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Field Name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Containing Class</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>CDIF Content Model</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Data Type(s)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Cardinality</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Enum/Const Values</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>cdi:index</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Physical Mapping Type</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>0..1</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Non-negative integer that orders the fields in the data structure (column number).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>cdi:format</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Physical Mapping Type</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>0..1</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>A format for number expressed as a string, or date format like YYYY/MM or MM-DD-YY.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>cdi:physicalDataType</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Physical Mapping Type</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0..1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>cdi:length</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Physical Mapping Type</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0..1</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>The column width if the tabular text is fixed width.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>cdi:nullSequence</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Physical Mapping Type</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0..1</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>The value of this property becomes the null annotation for the described column.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>cdi:defaultValue</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Physical Mapping Type</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0..1</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>A default string indicating the value to substitute for an empty string.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>cdi:scale</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Physical Mapping Type</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0..1</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>cdi:decimalPositions</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Physical Mapping Type</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0..1</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>cdi:minimumLength</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Physical Mapping Type</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0..1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>cdi:maximumLength</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Physical Mapping Type</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0..1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>cdi:isRequired</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Physical Mapping Type</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0..1</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>default: False</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>cdi:formats_InstanceVariable</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Physical Mapping Type</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>object reference</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0..1</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Reference to a variable defined in schema:variableMeasured.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1155,18 +3320,17 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>const | array of string</t>
+          <t>array of string</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1..*</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>const: schema:PropertyValue
-must contain: schema:PropertyValue</t>
+          <t>must contain: schema:PropertyValue</t>
         </is>
       </c>
     </row>
